--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>05/11 01:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>200</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>05/11 01:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>200</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>05/11 00:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>05/11 00:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>05/11 03:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>200</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>05/11 02:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>200</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>05/11 03:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>200</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>05/11 00:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>175</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>04/11 03:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>175</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>05/11 00:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>175</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>05/11 03:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>140</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>09/11 17:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>125</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>05/11 14:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>101</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>05/11 09:15</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>100</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>05/11 14:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>90</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>05/11 09:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>101</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>04/11 14:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>101</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>04/11 14:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>90</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>04/11 10:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>90</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>05/11 20:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F21" t="n">
+        <v>2.7</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>09/11 15:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>60</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>05/11 20:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2.6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>04/11 17:45</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
+      <c r="F24" t="n">
+        <v>4.4</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>05/11 17:45</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
+      <c r="F25" t="n">
+        <v>1.78</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>06/11 17:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>55</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,187 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45965.07314201198</v>
+        <v>45965.07314201389</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Basketball | X1re période[race to 25 regular time] | Milwaukee </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks – Toronto RaptorsNBA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>X1re période[race to 25 regular time]</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>05/11 00:40</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+25,7%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45965.13330645919</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Académico </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Académico de Viseu – Lusitania FC LourosaPortugal, Segunda Liga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>04/11 18:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+18,4%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45965.13330645919</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Dinamo Buc</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Dinamo Bucarest – FK Csikszereda Miercurea CiucLiga 1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>08/11 15:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+18,3%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45965.13330645919</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Racing Clu</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Racing Club – Defensa y JusticiaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>08/11 20:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+17,7%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45965.13330645919</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>05/11 00:40</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>30</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45965.13330645919</v>
+        <v>45965.13330645833</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>04/11 18:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>50</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45965.13330645919</v>
+        <v>45965.13330645833</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>08/11 15:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>60</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45965.13330645919</v>
+        <v>45965.13330645833</v>
       </c>
     </row>
     <row r="30">
@@ -1715,23 +1709,111 @@
           <t>08/11 20:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>60</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+17,7%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45965.13330645833</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sparta Prague – LiberecRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>09/11 17:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+90,7%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45965.18470741341</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | OFI Crète </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>OFI Crète – AEK Athènes385076e7 Super League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>09/11 15:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>+17,7%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>45965.13330645919</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+21,8%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45965.18470741341</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>09/11 17:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>125</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45965.18470741341</v>
+        <v>45965.18470741898</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>09/11 15:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>60</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,52 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45965.18470741341</v>
+        <v>45965.18470741898</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Partizan B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Partizan Belgrade – Novi PazarSuperLiga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>09/11 17:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+27,8%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45965.22360762263</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,23 +1838,66 @@
           <t>09/11 17:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="n">
+        <v>55</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+27,8%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45965.22360762732</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | FC Unirea </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FC Unirea 2004 Slobozia – CFR ClujLiga 1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>09/11 12:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>55.00</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>+27,8%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>45965.22360762263</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+17,8%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45965.27376501269</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>09/11 12:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>55</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,52 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45965.27376501269</v>
+        <v>45965.27376501157</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Corentin M</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Corentin Moutet – Aleksandar VukicATP - Metz</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>04/11 14:10</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>30,3%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+36,2%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45965.3067618884</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>04/11 14:10</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F35" t="n">
+        <v>4.5</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,97 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45965.3067618884</v>
+        <v>45965.30676188658</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 2.52e équipe | Differdang</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Differdange 03 – Rodange 91Luxembourg - Luxembourg Division 1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>05/11 18:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+15,4%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45965.35502448106</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Remplaçant marque un but: Oui | Inter Mila</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Inter Milan – Kairat AlmatyLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Remplaçant marque un but: Oui</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>05/11 20:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>50,9%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+14,5%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45965.35502448106</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>05/11 18:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>40</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45965.35502448106</v>
+        <v>45965.35502447917</v>
       </c>
     </row>
     <row r="37">
@@ -2012,10 +2010,8 @@
           <t>05/11 20:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F37" t="n">
+        <v>2.25</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2028,7 +2024,97 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45965.35502448106</v>
+        <v>45965.35502447917</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | VEG GKnigh</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VEG GKnights – DET Red WingsEtats-Unis - NHL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>05/11 03:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,30%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+29,6%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45965.39297389067</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | NY Rangers</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NY Rangers – CAR HurricanesEtats-Unis - NHL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>05/11 00:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+27,0%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45965.39297389067</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,10 +2053,8 @@
           <t>05/11 03:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>100</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45965.39297389067</v>
+        <v>45965.39297388889</v>
       </c>
     </row>
     <row r="39">
@@ -2098,10 +2096,8 @@
           <t>05/11 00:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>100</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2114,7 +2110,52 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45965.39297389067</v>
+        <v>45965.39297388889</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | X - aces | Kyrian Jac</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Kyrian Jacquet – Luca van AsscheATP - Metz</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>04/11 11:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+22,5%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45965.43510116267</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>04/11 11:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
+      <c r="F40" t="n">
+        <v>8.5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,97 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45965.43510116267</v>
+        <v>45965.43510115741</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CS Maritim</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CS Maritimo – FC Pacos FerreiraPortugal, Segunda Liga</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>09/11 15:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,70%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+62,0%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45965.47248946261</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Volleyball | 11-21er set | Janta Vole</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Janta Volej Women – Volero Le Cannet WomenLigue des Champions - Éliminatoires - Femmes</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>11-21er set</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>04/11 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>10,1%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+21,3%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45965.47248946261</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>09/11 15:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>60</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45965.47248946261</v>
+        <v>45965.47248946759</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>04/11 17:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>12</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,637 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45965.47248946261</v>
+        <v>45965.47248946759</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PMU(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PMU(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sparta Prague – Bili Tygri LiberecHockey européen . Rép. tchèque - Extraliga</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>09/11 17:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+45,6%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | MON Canadi</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MON Canadiens – PHI FlyersEtats-Unis - NHL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>05/11 00:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+35,8%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Hockey | Pas de buts | ANA Ducks </t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ANA Ducks – FLO PanthersEtats-Unis - NHL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>05/11 03:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+35,2%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Pénalité marquée: Non | Inter Mila</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Inter Milan – Kairat AlmatyEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pénalité marquée: Non</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>05/11 20:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>69,9%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+4,79%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 - tir cadré | Portsmouth</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Portsmouth FC – Wrexham AFCAngleterre. Championship</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>05/11 20:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+4,50%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey | Pas de buts | New York R</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New York Rangers – Carolina HurricanesÉtats-Unis - NHL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>05/11 00:10</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>75.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+2,31%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Football | Plus que 12.5 - tir cadré | Liverpool </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Liverpool – Real MadridEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 12.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>04/11 20:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+2,19%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 2.5 - tir cadré2e équipe | Atletico M</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Atletico Madrid – Union Saint-GilloiseEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 2.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>04/11 20:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>65,7%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+1,86%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tirs2e équipe | Manchester</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Manchester City – Borussia DortmundEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>05/11 20:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+1,30%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 15.5 - tirs1re équipe | Sporting B</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Sporting Braga – GenkEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Moins que 15.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>06/11 20:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>61,2%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+1,05%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 2.52e équipe | Atletico B</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga – Deportivo La EquidadColombie - Colombie Primera A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>09/11 01:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+0,66%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 6.5 - tirs1re équipe | Slavia Pra</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Slavia Prague – ArsenalEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>04/11 17:45</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+0,40%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football | Pénalité marquée: Non | Club Bruge</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Club Bruges – FC BarceloneCoupes d'Europe - ChampionsLeague</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pénalité marquée: Non</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>05/11 20:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>71,7%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+0,34%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45965.53455865777</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 7.5 - tir cadré | Bodø/Glimt</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Bodø/Glimt – MonacoEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>04/11 20:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>29,5%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+0,15%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45965.53455865777</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,8 @@
           <t>09/11 17:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>100</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="44">
@@ -2313,10 +2311,8 @@
           <t>05/11 00:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>100</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2329,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="45">
@@ -2358,10 +2354,8 @@
           <t>05/11 03:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>100</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2374,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="46">
@@ -2403,10 +2397,8 @@
           <t>05/11 20:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="F46" t="n">
+        <v>1.5</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2419,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="47">
@@ -2448,10 +2440,8 @@
           <t>05/11 20:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F47" t="n">
+        <v>2.7</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2464,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="48">
@@ -2493,10 +2483,8 @@
           <t>05/11 00:10</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>75</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2509,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="49">
@@ -2538,10 +2526,8 @@
           <t>04/11 20:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="F49" t="n">
+        <v>3.25</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2554,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="50">
@@ -2583,10 +2569,8 @@
           <t>04/11 20:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="F50" t="n">
+        <v>1.55</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2599,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="51">
@@ -2628,10 +2612,8 @@
           <t>05/11 20:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F51" t="n">
+        <v>3.3</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2644,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="52">
@@ -2673,10 +2655,8 @@
           <t>06/11 20:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="F52" t="n">
+        <v>1.65</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2689,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="53">
@@ -2718,10 +2698,8 @@
           <t>09/11 01:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>45</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2734,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="54">
@@ -2763,10 +2741,8 @@
           <t>04/11 17:45</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F54" t="n">
+        <v>2.5</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2779,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="55">
@@ -2808,10 +2784,8 @@
           <t>05/11 20:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="F55" t="n">
+        <v>1.4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2824,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
       </c>
     </row>
     <row r="56">
@@ -2853,10 +2827,8 @@
           <t>04/11 20:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F56" t="n">
+        <v>3.4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2869,7 +2841,187 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45965.53455865777</v>
+        <v>45965.5345586574</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PMU(FR)Hockey | X [№ 2 regular time] | Buffalo Sa</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PMU(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Buffalo Sabres – Utah MammothHockey US. NHL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>X [№ 2 regular time]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>05/11 00:10</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+71,4%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45965.56634005535</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Bnei Sakhn</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Bnei Sakhnin FC – Maccabi HaifaPremier League</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>08/11 15:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+48,8%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45965.56634005535</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Anaheim Du</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Anaheim Ducks – Florida PanthersUSA - NHL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>05/11 03:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+43,3%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45965.56634005535</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.51re équipe | Slavia Pra</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Slavia Prague – ArsenalLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>04/11 17:45</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+27,5%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45965.56634005535</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>05/11 00:10</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>50</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45965.56634005535</v>
+        <v>45965.56634005787</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>08/11 15:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>65</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45965.56634005535</v>
+        <v>45965.56634005787</v>
       </c>
     </row>
     <row r="59">
@@ -2960,10 +2956,8 @@
           <t>05/11 03:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>101</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2976,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45965.56634005535</v>
+        <v>45965.56634005787</v>
       </c>
     </row>
     <row r="60">
@@ -3005,23 +2999,156 @@
           <t>04/11 17:45</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" t="n">
+        <v>55</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+27,5%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45965.56634005787</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Pescara – </t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Pescara – AC MonzaSerie B</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>09/11 16:15</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>55.00</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>+27,5%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>45965.56634005535</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+13,2%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45965.59953539148</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set2e participant | Vitaliy Sa</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Vitaliy Sachko – Alexander BublikATP 250 Metz</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>05/11 11:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+12,2%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45965.59953539148</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X1re période[race to 25 regular time] | Orlando Ma</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Orlando Magic – Atlanta HawksNBA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>X1re période[race to 25 regular time]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>05/11 01:10</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+11,3%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45965.59953539148</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>09/11 16:15</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>55</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45965.59953539148</v>
+        <v>45965.59953539352</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>05/11 11:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="F62" t="n">
+        <v>7.5</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45965.59953539148</v>
+        <v>45965.59953539352</v>
       </c>
     </row>
     <row r="63">
@@ -3132,10 +3128,8 @@
           <t>05/11 01:10</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>19</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3148,7 +3142,367 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45965.59953539148</v>
+        <v>45965.59953539352</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | New York R</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>New York Rangers – Carolina HurricanesUSA - NHL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>05/11 00:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+78,8%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45965.64253708203</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey | Pas de buts | Calgary Fl</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Calgary Flames – Columbus Blue JacketsÉtats-Unis - NHL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>06/11 02:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+53,8%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45965.64253708203</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey | Pas de buts | Toronto Ma</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Toronto Maple Leafs – Utah MammothÉtats-Unis - NHL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>06/11 00:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+48,3%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45965.64253708203</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 2.51re équipe | Slavia Pra</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Slavia Prague – ArsenalEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>04/11 17:45</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+47,2%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45965.64253708203</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey | Pas de buts | Washington</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Washington Capitals – St. Louis BluesÉtats-Unis - NHL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>06/11 00:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>85.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+46,2%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45965.64253708203</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Vegas Gold</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Vegas Golden Knights – Détroit Red WingsUSA - NHL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>05/11 03:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+33,0%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45965.64253708203</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Oleksan</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FK Oleksandria – FC Polissya ZhytomyrUPL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>09/11 11:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+26,0%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45965.64253708203</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Kudrivk</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FK Kudrivka – Kolos KovalivkaUPL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>07/11 16:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+21,9%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45965.64253708203</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,10 +3171,8 @@
           <t>05/11 00:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>101</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3187,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45965.64253708203</v>
+        <v>45965.64253708333</v>
       </c>
     </row>
     <row r="65">
@@ -3216,10 +3214,8 @@
           <t>06/11 02:30</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>90</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3232,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45965.64253708203</v>
+        <v>45965.64253708333</v>
       </c>
     </row>
     <row r="66">
@@ -3261,10 +3257,8 @@
           <t>06/11 00:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>90</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3277,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45965.64253708203</v>
+        <v>45965.64253708333</v>
       </c>
     </row>
     <row r="67">
@@ -3306,10 +3300,8 @@
           <t>04/11 17:45</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>65</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3322,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45965.64253708203</v>
+        <v>45965.64253708333</v>
       </c>
     </row>
     <row r="68">
@@ -3351,10 +3343,8 @@
           <t>06/11 00:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>85.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>85</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3367,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45965.64253708203</v>
+        <v>45965.64253708333</v>
       </c>
     </row>
     <row r="69">
@@ -3396,10 +3386,8 @@
           <t>05/11 03:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>101</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3412,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45965.64253708203</v>
+        <v>45965.64253708333</v>
       </c>
     </row>
     <row r="70">
@@ -3441,10 +3429,8 @@
           <t>09/11 11:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>55</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3457,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45965.64253708203</v>
+        <v>45965.64253708333</v>
       </c>
     </row>
     <row r="71">
@@ -3486,10 +3472,8 @@
           <t>07/11 16:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>55</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3502,7 +3486,277 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45965.64253708203</v>
+        <v>45965.64253708333</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Calgary Fl</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Calgary Flames – Columbus Blue JacketsNHL</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>06/11 02:30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+155%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45965.6860093081</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Washington</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Washington Capitals – St. Louis BluesNHL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>06/11 00:30</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+152%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45965.6860093081</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Toronto Ma</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Toronto Maple Leafs – Utah Hockey ClubNHL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>06/11 00:00</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+150%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45965.6860093081</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Vancouver </t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Vancouver Canucks – Chicago BlackhawksNHL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>06/11 03:00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+149%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45965.6860093081</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | Lokomotiv </t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Lokomotiv Iaroslavl – HC Spartak MoscouRussia - KHL</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>06/11 16:00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+50,1%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45965.6860093081</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Dinamo Min</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Dinamo Minsk – AK Bars KazanRussia - KHL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>06/11 16:10</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+43,8%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45965.6860093081</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,10 +3515,8 @@
           <t>06/11 02:30</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>200</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45965.6860093081</v>
+        <v>45965.68600930556</v>
       </c>
     </row>
     <row r="73">
@@ -3560,10 +3558,8 @@
           <t>06/11 00:30</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F73" t="n">
+        <v>200</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3576,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45965.6860093081</v>
+        <v>45965.68600930556</v>
       </c>
     </row>
     <row r="74">
@@ -3605,10 +3601,8 @@
           <t>06/11 00:00</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>200</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3621,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45965.6860093081</v>
+        <v>45965.68600930556</v>
       </c>
     </row>
     <row r="75">
@@ -3650,10 +3644,8 @@
           <t>06/11 03:00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>200</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3666,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45965.6860093081</v>
+        <v>45965.68600930556</v>
       </c>
     </row>
     <row r="76">
@@ -3695,10 +3687,8 @@
           <t>06/11 16:00</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>101</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3711,7 +3701,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45965.6860093081</v>
+        <v>45965.68600930556</v>
       </c>
     </row>
     <row r="77">
@@ -3740,10 +3730,8 @@
           <t>06/11 16:10</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>90</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3756,7 +3744,52 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45965.6860093081</v>
+        <v>45965.68600930556</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | HC Dynamo </t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HC Dynamo Moscou – HC Lada TogliattiRussia - KHL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>06/11 16:30</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+50,9%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45965.72078350441</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3773,10 +3773,8 @@
           <t>06/11 16:30</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F78" t="n">
+        <v>101</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3789,7 +3787,52 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45965.72078350441</v>
+        <v>45965.72078350694</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | CSKA Mosco</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CSKA Moscou – Torpedo Nijni NovgorodRussia - KHL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>06/11 16:30</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+51,7%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45965.77244927153</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -3816,10 +3816,8 @@
           <t>06/11 16:30</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F79" t="n">
+        <v>100</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3832,7 +3830,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45965.77244927153</v>
+        <v>45965.77244927084</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-04.xlsx
+++ b/data/valuebets_database_2025-11-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3833,6 +3833,51 @@
         <v>45965.77244927084</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PMU(FR)Hockey | X [№ 2 regular time] | Colorado A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PMU(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Colorado Avalanche – Tampa Bay LightningHockey US. NHL A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>X [№ 2 regular time]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>05/11 02:40</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+53,7%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45965.97258939972</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
